--- a/outputs/Sorghum_(red,_local)_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_(red,_local)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="89">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alarm</t>
@@ -838,10 +841,10 @@
         <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
         <v>78</v>
@@ -850,7 +853,7 @@
         <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s">
         <v>78</v>
@@ -865,7 +868,7 @@
         <v>78</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P2" t="s">
         <v>78</v>
@@ -880,10 +883,10 @@
         <v>78</v>
       </c>
       <c r="T2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s">
         <v>78</v>
@@ -892,94 +895,94 @@
         <v>78</v>
       </c>
       <c r="X2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s">
         <v>78</v>
       </c>
       <c r="Z2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -987,160 +990,160 @@
         <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s">
         <v>78</v>
       </c>
       <c r="V3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s">
         <v>78</v>
       </c>
       <c r="X3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s">
         <v>78</v>
       </c>
       <c r="Z3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="s">
         <v>78</v>
       </c>
       <c r="AD3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1148,7 +1151,7 @@
         <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -1157,22 +1160,22 @@
         <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K4" t="s">
         <v>78</v>
@@ -1181,28 +1184,28 @@
         <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
         <v>78</v>
       </c>
       <c r="Q4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s">
         <v>78</v>
       </c>
       <c r="T4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s">
         <v>78</v>
@@ -1226,7 +1229,7 @@
         <v>78</v>
       </c>
       <c r="AB4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s">
         <v>78</v>
@@ -1247,7 +1250,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ4" t="s">
         <v>78</v>
@@ -1259,34 +1262,34 @@
         <v>78</v>
       </c>
       <c r="AM4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT4" t="s">
         <v>78</v>
       </c>
       <c r="AU4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW4" t="s">
         <v>78</v>
@@ -1295,13 +1298,13 @@
         <v>78</v>
       </c>
       <c r="AY4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1309,61 +1312,61 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s">
         <v>78</v>
       </c>
       <c r="T5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s">
         <v>78</v>
@@ -1372,7 +1375,7 @@
         <v>78</v>
       </c>
       <c r="W5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s">
         <v>78</v>
@@ -1384,22 +1387,22 @@
         <v>78</v>
       </c>
       <c r="AA5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG5" t="s">
         <v>78</v>
@@ -1420,10 +1423,10 @@
         <v>78</v>
       </c>
       <c r="AM5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO5" t="s">
         <v>78</v>
@@ -1441,28 +1444,28 @@
         <v>78</v>
       </c>
       <c r="AT5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU5" t="s">
         <v>78</v>
       </c>
       <c r="AV5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW5" t="s">
         <v>78</v>
       </c>
       <c r="AX5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1470,85 +1473,85 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s">
         <v>78</v>
       </c>
       <c r="U6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X6" t="s">
         <v>78</v>
       </c>
       <c r="Y6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA6" t="s">
         <v>78</v>
       </c>
       <c r="AB6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC6" t="s">
         <v>78</v>
@@ -1557,13 +1560,13 @@
         <v>78</v>
       </c>
       <c r="AE6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF6" t="s">
         <v>78</v>
       </c>
       <c r="AG6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s">
         <v>78</v>
@@ -1572,25 +1575,25 @@
         <v>78</v>
       </c>
       <c r="AJ6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK6" t="s">
         <v>78</v>
       </c>
       <c r="AL6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM6" t="s">
         <v>78</v>
       </c>
       <c r="AN6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ6" t="s">
         <v>78</v>
@@ -1605,7 +1608,7 @@
         <v>78</v>
       </c>
       <c r="AU6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV6" t="s">
         <v>78</v>
@@ -1614,16 +1617,16 @@
         <v>78</v>
       </c>
       <c r="AX6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1631,112 +1634,112 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL7" t="s">
         <v>78</v>
@@ -1748,43 +1751,43 @@
         <v>78</v>
       </c>
       <c r="AO7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP7" t="s">
         <v>78</v>
       </c>
       <c r="AQ7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1792,55 +1795,55 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s">
         <v>78</v>
@@ -1858,13 +1861,13 @@
         <v>78</v>
       </c>
       <c r="X8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA8" t="s">
         <v>78</v>
@@ -1879,7 +1882,7 @@
         <v>78</v>
       </c>
       <c r="AE8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF8" t="s">
         <v>78</v>
@@ -1903,7 +1906,7 @@
         <v>78</v>
       </c>
       <c r="AM8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN8" t="s">
         <v>78</v>
@@ -1921,31 +1924,31 @@
         <v>78</v>
       </c>
       <c r="AS8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -1956,7 +1959,7 @@
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
         <v>78</v>
@@ -1974,16 +1977,16 @@
         <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s">
         <v>78</v>
       </c>
       <c r="K9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M9" t="s">
         <v>78</v>
@@ -1992,10 +1995,10 @@
         <v>78</v>
       </c>
       <c r="O9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="s">
         <v>78</v>
@@ -2007,19 +2010,19 @@
         <v>78</v>
       </c>
       <c r="T9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V9" t="s">
         <v>78</v>
       </c>
       <c r="W9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s">
         <v>78</v>
@@ -2031,13 +2034,13 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC9" t="s">
         <v>78</v>
       </c>
       <c r="AD9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE9" t="s">
         <v>78</v>
@@ -2049,64 +2052,64 @@
         <v>78</v>
       </c>
       <c r="AH9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN9" t="s">
         <v>78</v>
       </c>
       <c r="AO9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ9" t="s">
         <v>78</v>
       </c>
       <c r="AR9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2114,112 +2117,112 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
         <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL10" t="s">
         <v>78</v>
@@ -2228,7 +2231,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO10" t="s">
         <v>78</v>
@@ -2240,34 +2243,34 @@
         <v>78</v>
       </c>
       <c r="AR10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV10" t="s">
         <v>78</v>
       </c>
       <c r="AW10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2275,160 +2278,160 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN11" t="s">
         <v>78</v>
       </c>
       <c r="AO11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2436,112 +2439,112 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s">
         <v>78</v>
@@ -2556,7 +2559,7 @@
         <v>78</v>
       </c>
       <c r="AP12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ12" t="s">
         <v>78</v>
@@ -2565,16 +2568,16 @@
         <v>78</v>
       </c>
       <c r="AS12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT12" t="s">
         <v>78</v>
       </c>
       <c r="AU12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW12" t="s">
         <v>78</v>
@@ -2583,13 +2586,13 @@
         <v>78</v>
       </c>
       <c r="AY12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2612,7 +2615,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
         <v>78</v>
@@ -2624,7 +2627,7 @@
         <v>78</v>
       </c>
       <c r="K13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s">
         <v>78</v>
@@ -2636,10 +2639,10 @@
         <v>78</v>
       </c>
       <c r="O13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
@@ -2648,19 +2651,19 @@
         <v>78</v>
       </c>
       <c r="S13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U13" t="s">
         <v>78</v>
       </c>
       <c r="V13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X13" t="s">
         <v>78</v>
@@ -2669,13 +2672,13 @@
         <v>78</v>
       </c>
       <c r="Z13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s">
         <v>78</v>
       </c>
       <c r="AB13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC13" t="s">
         <v>78</v>
@@ -2684,7 +2687,7 @@
         <v>78</v>
       </c>
       <c r="AE13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF13" t="s">
         <v>78</v>
@@ -2693,22 +2696,22 @@
         <v>78</v>
       </c>
       <c r="AH13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK13" t="s">
         <v>78</v>
       </c>
       <c r="AL13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s">
         <v>78</v>
@@ -2723,7 +2726,7 @@
         <v>78</v>
       </c>
       <c r="AR13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS13" t="s">
         <v>78</v>
@@ -2735,22 +2738,22 @@
         <v>78</v>
       </c>
       <c r="AV13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW13" t="s">
         <v>78</v>
       </c>
       <c r="AX13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2770,64 +2773,64 @@
         <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s">
         <v>78</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s">
         <v>78</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" t="s">
         <v>78</v>
       </c>
       <c r="N14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O14" t="s">
         <v>78</v>
       </c>
       <c r="P14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R14" t="s">
         <v>78</v>
       </c>
       <c r="S14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T14" t="s">
         <v>78</v>
       </c>
       <c r="U14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W14" t="s">
         <v>78</v>
       </c>
       <c r="X14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z14" t="s">
         <v>78</v>
@@ -2836,7 +2839,7 @@
         <v>78</v>
       </c>
       <c r="AB14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC14" t="s">
         <v>78</v>
@@ -2851,7 +2854,7 @@
         <v>78</v>
       </c>
       <c r="AG14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s">
         <v>78</v>
@@ -2860,13 +2863,13 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s">
         <v>78</v>
       </c>
       <c r="AL14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s">
         <v>78</v>
@@ -2875,13 +2878,13 @@
         <v>78</v>
       </c>
       <c r="AO14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR14" t="s">
         <v>78</v>
@@ -2890,28 +2893,28 @@
         <v>78</v>
       </c>
       <c r="AT14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2919,19 +2922,19 @@
         <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
         <v>78</v>
@@ -2946,13 +2949,13 @@
         <v>78</v>
       </c>
       <c r="K15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L15" t="s">
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N15" t="s">
         <v>78</v>
@@ -2970,7 +2973,7 @@
         <v>78</v>
       </c>
       <c r="S15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T15" t="s">
         <v>78</v>
@@ -2982,13 +2985,13 @@
         <v>78</v>
       </c>
       <c r="W15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X15" t="s">
         <v>78</v>
       </c>
       <c r="Y15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s">
         <v>78</v>
@@ -3003,13 +3006,13 @@
         <v>78</v>
       </c>
       <c r="AD15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE15" t="s">
         <v>78</v>
       </c>
       <c r="AF15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG15" t="s">
         <v>78</v>
@@ -3021,7 +3024,7 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK15" t="s">
         <v>78</v>
@@ -3030,7 +3033,7 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s">
         <v>78</v>
@@ -3045,34 +3048,34 @@
         <v>78</v>
       </c>
       <c r="AR15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU15" t="s">
         <v>78</v>
       </c>
       <c r="AV15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW15" t="s">
         <v>78</v>
       </c>
       <c r="AX15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BA15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3080,7 +3083,7 @@
         <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
         <v>78</v>
@@ -3092,118 +3095,118 @@
         <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
         <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK16" t="s">
         <v>78</v>
       </c>
       <c r="AL16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR16" t="s">
         <v>78</v>
@@ -3212,7 +3215,7 @@
         <v>78</v>
       </c>
       <c r="AT16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU16" t="s">
         <v>78</v>
@@ -3221,19 +3224,19 @@
         <v>78</v>
       </c>
       <c r="AW16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX16" t="s">
         <v>78</v>
       </c>
       <c r="AY16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3241,43 +3244,43 @@
         <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O17" t="s">
         <v>78</v>
@@ -3286,7 +3289,7 @@
         <v>78</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R17" t="s">
         <v>78</v>
@@ -3295,7 +3298,7 @@
         <v>78</v>
       </c>
       <c r="T17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U17" t="s">
         <v>78</v>
@@ -3307,10 +3310,10 @@
         <v>78</v>
       </c>
       <c r="X17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s">
         <v>78</v>
@@ -3322,28 +3325,28 @@
         <v>78</v>
       </c>
       <c r="AC17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD17" t="s">
         <v>78</v>
       </c>
       <c r="AE17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK17" t="s">
         <v>78</v>
@@ -3361,25 +3364,25 @@
         <v>78</v>
       </c>
       <c r="AP17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS17" t="s">
         <v>78</v>
       </c>
       <c r="AT17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU17" t="s">
         <v>78</v>
       </c>
       <c r="AV17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW17" t="s">
         <v>78</v>
@@ -3388,13 +3391,13 @@
         <v>78</v>
       </c>
       <c r="AY17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3402,160 +3405,160 @@
         <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
         <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL18" t="s">
         <v>78</v>
       </c>
       <c r="AM18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3569,7 +3572,7 @@
         <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>78</v>
@@ -3590,7 +3593,7 @@
         <v>78</v>
       </c>
       <c r="K19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L19" t="s">
         <v>78</v>
@@ -3623,13 +3626,13 @@
         <v>78</v>
       </c>
       <c r="V19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W19" t="s">
         <v>78</v>
       </c>
       <c r="X19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s">
         <v>78</v>
@@ -3644,10 +3647,10 @@
         <v>78</v>
       </c>
       <c r="AC19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE19" t="s">
         <v>78</v>
@@ -3674,49 +3677,49 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ19" t="s">
         <v>78</v>
       </c>
       <c r="AR19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS19" t="s">
         <v>78</v>
       </c>
       <c r="AT19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU19" t="s">
         <v>78</v>
       </c>
       <c r="AV19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3724,7 +3727,7 @@
         <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
         <v>78</v>
@@ -3733,109 +3736,109 @@
         <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN20" t="s">
         <v>78</v>
@@ -3844,40 +3847,40 @@
         <v>78</v>
       </c>
       <c r="AP20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR20" t="s">
         <v>78</v>
       </c>
       <c r="AS20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT20" t="s">
         <v>78</v>
       </c>
       <c r="AU20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW20" t="s">
         <v>78</v>
       </c>
       <c r="AX20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3885,40 +3888,40 @@
         <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N21" t="s">
         <v>78</v>
@@ -3933,61 +3936,61 @@
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK21" t="s">
         <v>78</v>
@@ -3996,16 +3999,16 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO21" t="s">
         <v>78</v>
       </c>
       <c r="AP21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ21" t="s">
         <v>78</v>
@@ -4014,31 +4017,31 @@
         <v>78</v>
       </c>
       <c r="AS21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4046,16 +4049,16 @@
         <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
         <v>78</v>
@@ -4064,16 +4067,16 @@
         <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s">
         <v>78</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L22" t="s">
         <v>78</v>
@@ -4094,7 +4097,7 @@
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S22" t="s">
         <v>78</v>
@@ -4130,7 +4133,7 @@
         <v>78</v>
       </c>
       <c r="AD22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE22" t="s">
         <v>78</v>
@@ -4139,7 +4142,7 @@
         <v>78</v>
       </c>
       <c r="AG22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s">
         <v>78</v>
@@ -4148,7 +4151,7 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK22" t="s">
         <v>78</v>
@@ -4157,26 +4160,26 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN22" t="s">
         <v>78</v>
       </c>
       <c r="AO22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="s">
         <v>78</v>
       </c>
       <c r="AQ22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR22" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS22" t="s">
         <v>80</v>
       </c>
-      <c r="AS22" t="s">
-        <v>79</v>
-      </c>
       <c r="AT22" t="s">
         <v>78</v>
       </c>
@@ -4184,7 +4187,7 @@
         <v>78</v>
       </c>
       <c r="AV22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW22" t="s">
         <v>78</v>
@@ -4193,13 +4196,13 @@
         <v>78</v>
       </c>
       <c r="AY22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BA22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4213,13 +4216,13 @@
         <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
         <v>78</v>
@@ -4264,7 +4267,7 @@
         <v>78</v>
       </c>
       <c r="U23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V23" t="s">
         <v>78</v>
@@ -4273,7 +4276,7 @@
         <v>78</v>
       </c>
       <c r="X23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y23" t="s">
         <v>78</v>
@@ -4288,13 +4291,13 @@
         <v>78</v>
       </c>
       <c r="AC23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD23" t="s">
         <v>78</v>
       </c>
       <c r="AE23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="s">
         <v>78</v>
@@ -4315,52 +4318,52 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO23" t="s">
         <v>80</v>
       </c>
-      <c r="AN23" t="s">
+      <c r="AP23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT23" t="s">
         <v>80</v>
       </c>
-      <c r="AO23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AT23" t="s">
-        <v>79</v>
-      </c>
       <c r="AU23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV23" t="s">
         <v>78</v>
       </c>
       <c r="AW23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AZ23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4368,133 +4371,133 @@
         <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s">
         <v>78</v>
       </c>
       <c r="AK24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s">
         <v>78</v>
       </c>
       <c r="AO24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ24" t="s">
         <v>78</v>
       </c>
       <c r="AR24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS24" t="s">
         <v>78</v>
@@ -4503,25 +4506,25 @@
         <v>78</v>
       </c>
       <c r="AU24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4592,7 +4595,7 @@
         <v>78</v>
       </c>
       <c r="W25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X25" t="s">
         <v>78</v>
@@ -4604,7 +4607,7 @@
         <v>78</v>
       </c>
       <c r="AA25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB25" t="s">
         <v>78</v>
@@ -4616,7 +4619,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF25" t="s">
         <v>78</v>
@@ -4643,16 +4646,16 @@
         <v>78</v>
       </c>
       <c r="AN25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s">
         <v>78</v>
       </c>
       <c r="AQ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR25" t="s">
         <v>78</v>
@@ -4673,16 +4676,16 @@
         <v>78</v>
       </c>
       <c r="AX25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AZ25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:53">
@@ -4693,7 +4696,7 @@
         <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>78</v>
@@ -4702,106 +4705,106 @@
         <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s">
         <v>78</v>
@@ -4816,19 +4819,19 @@
         <v>78</v>
       </c>
       <c r="AR26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU26" t="s">
         <v>78</v>
       </c>
       <c r="AV26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW26" t="s">
         <v>78</v>
@@ -4837,13 +4840,13 @@
         <v>78</v>
       </c>
       <c r="AY26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AZ26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BA26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_(red,_local)_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_(red,_local)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="81">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -256,31 +256,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>10%</t>
   </si>
 </sst>
 </file>
@@ -832,7 +808,7 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
         <v>78</v>
@@ -847,10 +823,10 @@
         <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s">
         <v>79</v>
@@ -859,7 +835,7 @@
         <v>78</v>
       </c>
       <c r="L2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s">
         <v>78</v>
@@ -877,10 +853,10 @@
         <v>78</v>
       </c>
       <c r="R2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
         <v>79</v>
@@ -889,7 +865,7 @@
         <v>79</v>
       </c>
       <c r="V2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s">
         <v>78</v>
@@ -976,13 +952,13 @@
         <v>79</v>
       </c>
       <c r="AY2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1047,19 +1023,19 @@
         <v>79</v>
       </c>
       <c r="U3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
       </c>
       <c r="W3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X3" t="s">
         <v>79</v>
       </c>
       <c r="Y3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z3" t="s">
         <v>79</v>
@@ -1071,7 +1047,7 @@
         <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD3" t="s">
         <v>79</v>
@@ -1137,13 +1113,13 @@
         <v>79</v>
       </c>
       <c r="AY3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1232,16 +1208,16 @@
         <v>79</v>
       </c>
       <c r="AC4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
       </c>
       <c r="AF4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AG4" t="s">
         <v>78</v>
@@ -1298,13 +1274,13 @@
         <v>78</v>
       </c>
       <c r="AY4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1429,16 +1405,16 @@
         <v>79</v>
       </c>
       <c r="AO5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ5" t="s">
         <v>78</v>
       </c>
       <c r="AR5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS5" t="s">
         <v>78</v>
@@ -1459,13 +1435,13 @@
         <v>79</v>
       </c>
       <c r="AY5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1554,10 +1530,10 @@
         <v>79</v>
       </c>
       <c r="AC6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AE6" t="s">
         <v>79</v>
@@ -1572,7 +1548,7 @@
         <v>78</v>
       </c>
       <c r="AI6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ6" t="s">
         <v>79</v>
@@ -1596,13 +1572,13 @@
         <v>79</v>
       </c>
       <c r="AQ6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR6" t="s">
         <v>78</v>
       </c>
       <c r="AS6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT6" t="s">
         <v>78</v>
@@ -1620,13 +1596,13 @@
         <v>79</v>
       </c>
       <c r="AY6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1742,19 +1718,19 @@
         <v>79</v>
       </c>
       <c r="AL7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO7" t="s">
         <v>79</v>
       </c>
       <c r="AP7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ7" t="s">
         <v>79</v>
@@ -1781,13 +1757,13 @@
         <v>79</v>
       </c>
       <c r="AY7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1870,7 +1846,7 @@
         <v>79</v>
       </c>
       <c r="AA8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB8" t="s">
         <v>78</v>
@@ -1897,13 +1873,13 @@
         <v>78</v>
       </c>
       <c r="AJ8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM8" t="s">
         <v>79</v>
@@ -1942,13 +1918,13 @@
         <v>79</v>
       </c>
       <c r="AY8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2031,7 +2007,7 @@
         <v>78</v>
       </c>
       <c r="AA9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB9" t="s">
         <v>79</v>
@@ -2049,7 +2025,7 @@
         <v>78</v>
       </c>
       <c r="AG9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s">
         <v>79</v>
@@ -2103,13 +2079,13 @@
         <v>79</v>
       </c>
       <c r="AY9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2225,7 +2201,7 @@
         <v>79</v>
       </c>
       <c r="AL10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM10" t="s">
         <v>78</v>
@@ -2237,10 +2213,10 @@
         <v>78</v>
       </c>
       <c r="AP10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR10" t="s">
         <v>79</v>
@@ -2255,7 +2231,7 @@
         <v>79</v>
       </c>
       <c r="AV10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW10" t="s">
         <v>79</v>
@@ -2264,13 +2240,13 @@
         <v>79</v>
       </c>
       <c r="AY10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2392,7 +2368,7 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
@@ -2425,13 +2401,13 @@
         <v>79</v>
       </c>
       <c r="AY11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2550,28 +2526,28 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP12" t="s">
         <v>79</v>
       </c>
       <c r="AQ12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS12" t="s">
         <v>79</v>
       </c>
       <c r="AT12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU12" t="s">
         <v>79</v>
@@ -2580,19 +2556,19 @@
         <v>79</v>
       </c>
       <c r="AW12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX12" t="s">
         <v>78</v>
       </c>
       <c r="AY12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2723,7 +2699,7 @@
         <v>78</v>
       </c>
       <c r="AQ13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR13" t="s">
         <v>79</v>
@@ -2735,7 +2711,7 @@
         <v>78</v>
       </c>
       <c r="AU13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV13" t="s">
         <v>79</v>
@@ -2747,13 +2723,13 @@
         <v>79</v>
       </c>
       <c r="AY13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2848,7 +2824,7 @@
         <v>78</v>
       </c>
       <c r="AE14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF14" t="s">
         <v>78</v>
@@ -2857,7 +2833,7 @@
         <v>79</v>
       </c>
       <c r="AH14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s">
         <v>78</v>
@@ -2890,13 +2866,13 @@
         <v>78</v>
       </c>
       <c r="AS14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT14" t="s">
         <v>79</v>
       </c>
       <c r="AU14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AV14" t="s">
         <v>79</v>
@@ -2905,16 +2881,16 @@
         <v>79</v>
       </c>
       <c r="AX14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AZ14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -3012,7 +2988,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AG15" t="s">
         <v>78</v>
@@ -3069,13 +3045,13 @@
         <v>79</v>
       </c>
       <c r="AY15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="BA15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3086,19 +3062,19 @@
         <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
         <v>79</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
         <v>79</v>
@@ -3188,7 +3164,7 @@
         <v>79</v>
       </c>
       <c r="AK16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s">
         <v>79</v>
@@ -3209,34 +3185,34 @@
         <v>79</v>
       </c>
       <c r="AR16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT16" t="s">
         <v>79</v>
       </c>
       <c r="AU16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AW16" t="s">
         <v>79</v>
       </c>
       <c r="AX16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AY16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3295,7 +3271,7 @@
         <v>78</v>
       </c>
       <c r="S17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T17" t="s">
         <v>79</v>
@@ -3304,7 +3280,7 @@
         <v>78</v>
       </c>
       <c r="V17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W17" t="s">
         <v>78</v>
@@ -3349,7 +3325,7 @@
         <v>79</v>
       </c>
       <c r="AK17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL17" t="s">
         <v>78</v>
@@ -3361,7 +3337,7 @@
         <v>78</v>
       </c>
       <c r="AO17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP17" t="s">
         <v>79</v>
@@ -3385,19 +3361,19 @@
         <v>79</v>
       </c>
       <c r="AW17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX17" t="s">
         <v>78</v>
       </c>
       <c r="AY17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3408,7 +3384,7 @@
         <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -3513,7 +3489,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s">
         <v>79</v>
@@ -3552,13 +3528,13 @@
         <v>79</v>
       </c>
       <c r="AY18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3677,13 +3653,13 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AN19" t="s">
         <v>79</v>
       </c>
       <c r="AO19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AP19" t="s">
         <v>79</v>
@@ -3692,7 +3668,7 @@
         <v>78</v>
       </c>
       <c r="AR19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AS19" t="s">
         <v>78</v>
@@ -3704,22 +3680,22 @@
         <v>78</v>
       </c>
       <c r="AV19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AW19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AX19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AY19" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AZ19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA19" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3730,7 +3706,7 @@
         <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>78</v>
@@ -3844,7 +3820,7 @@
         <v>78</v>
       </c>
       <c r="AO20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP20" t="s">
         <v>79</v>
@@ -3853,13 +3829,13 @@
         <v>79</v>
       </c>
       <c r="AR20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS20" t="s">
         <v>79</v>
       </c>
       <c r="AT20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU20" t="s">
         <v>79</v>
@@ -3868,19 +3844,19 @@
         <v>79</v>
       </c>
       <c r="AW20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX20" t="s">
         <v>79</v>
       </c>
       <c r="AY20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3927,10 +3903,10 @@
         <v>78</v>
       </c>
       <c r="O21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q21" t="s">
         <v>78</v>
@@ -3993,7 +3969,7 @@
         <v>79</v>
       </c>
       <c r="AK21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s">
         <v>78</v>
@@ -4011,10 +3987,10 @@
         <v>79</v>
       </c>
       <c r="AQ21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS21" t="s">
         <v>79</v>
@@ -4035,13 +4011,13 @@
         <v>79</v>
       </c>
       <c r="AY21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4160,13 +4136,13 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s">
         <v>78</v>
       </c>
       <c r="AO22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s">
         <v>78</v>
@@ -4175,10 +4151,10 @@
         <v>79</v>
       </c>
       <c r="AR22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AS22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AT22" t="s">
         <v>78</v>
@@ -4187,7 +4163,7 @@
         <v>78</v>
       </c>
       <c r="AV22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AW22" t="s">
         <v>78</v>
@@ -4196,13 +4172,13 @@
         <v>78</v>
       </c>
       <c r="AY22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AZ22" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="BA22" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4297,7 +4273,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF23" t="s">
         <v>78</v>
@@ -4321,13 +4297,13 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AO23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AP23" t="s">
         <v>78</v>
@@ -4342,7 +4318,7 @@
         <v>78</v>
       </c>
       <c r="AT23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AU23" t="s">
         <v>79</v>
@@ -4357,13 +4333,13 @@
         <v>79</v>
       </c>
       <c r="AY23" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AZ23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="BA23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4473,7 +4449,7 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK24" t="s">
         <v>79</v>
@@ -4485,7 +4461,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s">
         <v>79</v>
@@ -4494,16 +4470,16 @@
         <v>79</v>
       </c>
       <c r="AQ24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR24" t="s">
         <v>79</v>
       </c>
       <c r="AS24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AT24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AU24" t="s">
         <v>79</v>
@@ -4518,13 +4494,13 @@
         <v>79</v>
       </c>
       <c r="AY24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4646,16 +4622,16 @@
         <v>78</v>
       </c>
       <c r="AN25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AO25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AP25" t="s">
         <v>78</v>
       </c>
       <c r="AQ25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AR25" t="s">
         <v>78</v>
@@ -4679,13 +4655,13 @@
         <v>79</v>
       </c>
       <c r="AY25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AZ25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:53">
@@ -4813,10 +4789,10 @@
         <v>78</v>
       </c>
       <c r="AP26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AR26" t="s">
         <v>79</v>
@@ -4828,25 +4804,25 @@
         <v>79</v>
       </c>
       <c r="AU26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AV26" t="s">
         <v>79</v>
       </c>
       <c r="AW26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AX26" t="s">
         <v>78</v>
       </c>
       <c r="AY26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AZ26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="BA26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_(red,_local)_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_(red,_local)_tukey_classification_matrix.xlsx
@@ -250,7 +250,7 @@
     <t>Yambio</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
